--- a/backend/school-entry/src/main/resources/templates/import/SchoolListTemplate.xlsx
+++ b/backend/school-entry/src/main/resources/templates/import/SchoolListTemplate.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -52,10 +52,16 @@
     <t xml:space="preserve">Telefonnummer</t>
   </si>
   <si>
+    <t xml:space="preserve">E-Mail-Adresse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eingangsstufe (Ja = X)</t>
   </si>
   <si>
     <t xml:space="preserve">Frühe Untersuchung (Ja = X)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bemerkung</t>
   </si>
 </sst>
 </file>
@@ -156,8 +162,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -195,6 +201,12 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
